--- a/data/input_emails.xlsx
+++ b/data/input_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sourav/Personal/Projects/DeployedProjects/InterviewEmail/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1849B2-6EC1-DC40-8D57-7D0EFACB6765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD532E18-41CA-8A40-AC57-740429BC1081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="680" windowWidth="29900" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>email</t>
   </si>
   <si>
-    <t>srvgarg01@gmail.com</t>
+    <t>abc@gmail.com</t>
   </si>
 </sst>
 </file>
